--- a/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 17,74</t>
+          <t>-0,84; 18,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,07</t>
+          <t>-4,13; 7,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 13,35</t>
+          <t>-0,36; 11,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,36</t>
+          <t>-0,89; 7,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 4,41</t>
+          <t>-3,25; 4,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,19</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 0,0</t>
+          <t>-11,56; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 0,0</t>
+          <t>-10,09; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 0,0</t>
+          <t>-10,55; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -1,86</t>
+          <t>-14,24; -1,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 7,17</t>
+          <t>0,42; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,0</t>
+          <t>-2,66; 2,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,44</t>
+          <t>-2,55; 1,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 1034,65</t>
+          <t>-15,6; 1149,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,03; 267,22</t>
+          <t>-80,37; 296,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 18,02</t>
+          <t>-0,73; 17,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 7,08</t>
+          <t>-3,52; 6,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 11,69</t>
+          <t>-0,14; 12,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,02</t>
+          <t>-1,16; 6,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,5</t>
+          <t>-3,37; 4,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 18,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 0,0</t>
+          <t>-9,07; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 0,0</t>
+          <t>-10,17; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 0,0</t>
+          <t>-10,92; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,24; -1,78</t>
+          <t>-15,88; -1,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,81</t>
+          <t>0,1; 7,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,2</t>
+          <t>-2,81; 1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,45</t>
+          <t>-2,34; 1,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 1149,58</t>
+          <t>-26,19; 921,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 296,93</t>
+          <t>-81,02; 224,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 17,51</t>
+          <t>-1,08; 17,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,63</t>
+          <t>-3,68; 6,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,39</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 12,13</t>
+          <t>-0,17; 13,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,76</t>
+          <t>-1,11; 6,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 4,61</t>
+          <t>-4,06; 4,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,17</t>
+          <t>0,0; 17,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,0</t>
+          <t>-10,15; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 0,0</t>
+          <t>-12,96; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 0,0</t>
+          <t>-11,67; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,88; -1,85</t>
+          <t>-14,59; -1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,33</t>
+          <t>0,23; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,84</t>
+          <t>-2,73; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,56</t>
+          <t>-2,4; 1,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 921,61</t>
+          <t>-18,0; 1034,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 224,58</t>
+          <t>-80,03; 267,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>312,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>101,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>2.044160225278595</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5530010772600512</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4657672456798365</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>3.620048818971512</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.9057800013566677</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,116 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,08; 17,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 6,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,99</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.1683240724022111</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.494643027147591</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.082309705250116</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.293548376258634</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.682926334488333</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>362,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>178,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>60,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 13,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,11; 6,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 4,41</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.8382546915123412</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4307852420531451</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2887757990721698</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2.932769649201985</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.772051059345614</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.124272587795453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.1549176612504611</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.2944156540842893</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.2583446707025998</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,19</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,15; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-12,96; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.366933854835052</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.920941960103516</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.62428907649714</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +745,211 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-5,85</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.9255222931606506</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.4135067782709107</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.7420913646093932</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-11,67; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-14,59; -1,86</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.499321907477138</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.792078288575574</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.162656492990689</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.6351839778925888</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.062767403637553</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.92074081985727</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.875910864769285</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.3353646040479404</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187,04%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-17,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-22,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 7,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 2,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 1,44</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-18,0; 1034,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-80,03; 267,22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.6216972025075763</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.08204580963323541</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.02673525807112931</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1.652150151299655</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1503399011240426</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.09656382904025769</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.05467612923172458</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.666113260052693</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.4986557574116259</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.2285161137855906</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7963926186874642</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.325547767870172</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.524977063116544</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3360738048872841</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>10.98124204969509</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.530104026763215</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +958,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
